--- a/rag_data/agents.xlsx
+++ b/rag_data/agents.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,37 +441,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>35717bd6-7960-4e4d-b413-6947bd484792</t>
+          <t>84cac9be-3a0b-407f-93bb-41e578c22776</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sales report</t>
+          <t>dce</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-06-03T14:58:45.188791</t>
+          <t>2026-06-10T16:48:22.885426</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9bdb3b9d-c26b-4972-a254-98b7b029c6df</t>
+          <t>5638ed57-5bf9-492a-9e7c-a939b80ba6af</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>dce technology</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-06-03T15:10:17.777219</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>2026-06-12T16:21:02.192342</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>b92eff0b-1132-4d4e-8eb9-d8ebf16b5e83</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sales data</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-06-12T16:24:45.830463</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0b96fe8c-7dc8-4af2-aeae-ea8f36294abe</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>new  file</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-06-12T16:27:16.378973</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
